--- a/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>BFST</t>
   </si>
@@ -656,112 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>353300</v>
+      </c>
+      <c r="E8" s="3">
         <v>236100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>170400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>149800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>103500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>76200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>51600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>43400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>38600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>27500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>29000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -801,9 +807,12 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -843,9 +852,12 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,9 +961,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,24 +1006,27 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E15" s="3">
         <v>-6900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>-5800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>-4300</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1042,8 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E17" s="3">
         <v>47400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>210600</v>
+      </c>
+      <c r="E18" s="3">
         <v>188700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>145800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>127600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>77600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>59800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>40100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>36400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23500</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,8 +1179,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1156,83 +1189,89 @@
         <v>-120100</v>
       </c>
       <c r="E20" s="3">
+        <v>-120100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-81300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-90900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-47700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-42500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-31200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-29600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-27300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-17400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17900</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E21" s="3">
         <v>73400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>68700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1272,93 +1311,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E23" s="3">
         <v>68600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>64600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>29900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5600</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E24" s="3">
         <v>14300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E26" s="3">
         <v>54300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>52100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>30000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E27" s="3">
         <v>52900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>52100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>30000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1539,36 +1599,39 @@
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1700</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>500</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,9 +1716,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1660,83 +1729,89 @@
         <v>120100</v>
       </c>
       <c r="E32" s="3">
+        <v>120100</v>
+      </c>
+      <c r="F32" s="3">
         <v>81300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>90900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>47700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>42500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>31200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>29600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>27300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>17400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17900</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E33" s="3">
         <v>52900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>52100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>30000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E35" s="3">
         <v>52900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>52100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>30000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,92 +1987,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>226100</v>
+      </c>
+      <c r="E41" s="3">
         <v>152700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>149100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>107600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>185100</v>
+      </c>
+      <c r="E42" s="3">
         <v>53100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>243700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>186800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>73900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>51100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2027,9 +2119,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,9 +2164,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2111,9 +2209,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2153,9 +2254,12 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2195,81 +2299,87 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E48" s="3">
         <v>63200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>58200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>58600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E49" s="3">
         <v>102600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>72100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>63600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>55200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>57400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2279,9 +2389,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,30 +2479,33 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E52" s="3">
         <v>31200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3800</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2402,12 +2521,15 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6584600</v>
+      </c>
+      <c r="E54" s="3">
         <v>5990500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4726400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4160400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2273800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2094900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1321300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1105800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1076100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>684500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>684200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,50 +2655,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>900</v>
       </c>
       <c r="J57" s="3">
         <v>900</v>
       </c>
       <c r="K57" s="3">
+        <v>900</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2609,9 +2742,12 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2624,12 +2760,12 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>13200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,15 +2781,18 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2693,36 +2832,39 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E61" s="3">
         <v>115700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>25000</v>
       </c>
       <c r="H61" s="3">
         <v>25000</v>
       </c>
       <c r="I61" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J61" s="3">
         <v>2700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2735,9 +2877,12 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2777,9 +2922,12 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5940300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5410000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4293000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3750400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1988700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1834800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1141300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>992300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>963600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>605700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>612300</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3057,7 +3224,7 @@
         <v>71900</v>
       </c>
       <c r="E70" s="3">
-        <v>0</v>
+        <v>71900</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E72" s="3">
         <v>164000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>121900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>79200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>56700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>38000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>572400</v>
+      </c>
+      <c r="E76" s="3">
         <v>508600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>433400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>410000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>285100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>260100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>179900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>113600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>112400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>71900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E81" s="3">
         <v>52900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>52100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>30000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1200</v>
       </c>
       <c r="I83" s="3">
         <v>1200</v>
       </c>
       <c r="J83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>800</v>
       </c>
       <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>800</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E89" s="3">
         <v>69600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>56400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-521100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-675400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-475300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-192300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-170300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-153400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>16000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,29 +4221,30 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-12200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-9400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-7500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-5100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-3300</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>502100</v>
+      </c>
+      <c r="E100" s="3">
         <v>715300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>538200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>505700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>161200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>139500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>210900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>26500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>25600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4234,55 +4482,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E102" s="3">
         <v>84400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-80800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>59800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>65400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>BFST</t>
   </si>
@@ -727,25 +727,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>353300</v>
+        <v>245800</v>
       </c>
       <c r="E8" s="3">
-        <v>236100</v>
+        <v>218000</v>
       </c>
       <c r="F8" s="3">
-        <v>170400</v>
+        <v>181600</v>
       </c>
       <c r="G8" s="3">
-        <v>149800</v>
+        <v>137800</v>
       </c>
       <c r="H8" s="3">
-        <v>103500</v>
+        <v>88300</v>
       </c>
       <c r="I8" s="3">
-        <v>76200</v>
+        <v>67600</v>
       </c>
       <c r="J8" s="3">
-        <v>51600</v>
+        <v>45800</v>
       </c>
       <c r="K8" s="3">
         <v>43400</v>
@@ -816,26 +816,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>245800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>218000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>181600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>137800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>88300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>67600</v>
+      </c>
+      <c r="J10" s="3">
+        <v>45800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-6800</v>
+        <v>4700</v>
       </c>
       <c r="E15" s="3">
-        <v>-6900</v>
+        <v>4800</v>
       </c>
       <c r="F15" s="3">
-        <v>-5800</v>
+        <v>4200</v>
       </c>
       <c r="G15" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>4400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1500</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>142700</v>
+        <v>156500</v>
       </c>
       <c r="E17" s="3">
-        <v>47400</v>
+        <v>143700</v>
       </c>
       <c r="F17" s="3">
-        <v>24600</v>
+        <v>115000</v>
       </c>
       <c r="G17" s="3">
-        <v>22100</v>
+        <v>91400</v>
       </c>
       <c r="H17" s="3">
-        <v>25900</v>
+        <v>57700</v>
       </c>
       <c r="I17" s="3">
-        <v>16400</v>
+        <v>46700</v>
       </c>
       <c r="J17" s="3">
-        <v>11500</v>
+        <v>36700</v>
       </c>
       <c r="K17" s="3">
         <v>7000</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>210600</v>
+        <v>89400</v>
       </c>
       <c r="E18" s="3">
-        <v>188700</v>
+        <v>74300</v>
       </c>
       <c r="F18" s="3">
-        <v>145800</v>
+        <v>66600</v>
       </c>
       <c r="G18" s="3">
-        <v>127600</v>
+        <v>46300</v>
       </c>
       <c r="H18" s="3">
-        <v>77600</v>
+        <v>30600</v>
       </c>
       <c r="I18" s="3">
-        <v>59800</v>
+        <v>20900</v>
       </c>
       <c r="J18" s="3">
-        <v>40100</v>
+        <v>9100</v>
       </c>
       <c r="K18" s="3">
         <v>36400</v>
@@ -1185,26 +1185,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-120100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-120100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-81300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-90900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-47700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-42500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-31200</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>-29600</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>95300</v>
+        <v>94000</v>
       </c>
       <c r="E21" s="3">
-        <v>73400</v>
+        <v>79100</v>
       </c>
       <c r="F21" s="3">
-        <v>68700</v>
+        <v>70800</v>
       </c>
       <c r="G21" s="3">
-        <v>39900</v>
+        <v>50700</v>
       </c>
       <c r="H21" s="3">
-        <v>31400</v>
+        <v>33100</v>
       </c>
       <c r="I21" s="3">
-        <v>18500</v>
+        <v>22700</v>
       </c>
       <c r="J21" s="3">
-        <v>10100</v>
+        <v>10500</v>
       </c>
       <c r="K21" s="3">
         <v>8000</v>
@@ -1275,26 +1275,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>3300</v>
       </c>
       <c r="J24" s="3">
-        <v>2400</v>
+        <v>4100</v>
       </c>
       <c r="K24" s="3">
         <v>1600</v>
@@ -1474,7 +1474,7 @@
         <v>14100</v>
       </c>
       <c r="J26" s="3">
-        <v>6500</v>
+        <v>4800</v>
       </c>
       <c r="K26" s="3">
         <v>5100</v>
@@ -1519,7 +1519,7 @@
         <v>14100</v>
       </c>
       <c r="J27" s="3">
-        <v>6500</v>
+        <v>4800</v>
       </c>
       <c r="K27" s="3">
         <v>5100</v>
@@ -1590,17 +1590,17 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-1700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1725,26 +1725,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>120100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>120100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>81300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>90900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>47700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>42500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>31200</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>29600</v>
@@ -1771,10 +1771,10 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>65600</v>
+        <v>71000</v>
       </c>
       <c r="E33" s="3">
-        <v>52900</v>
+        <v>54300</v>
       </c>
       <c r="F33" s="3">
         <v>52100</v>
@@ -1861,10 +1861,10 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>65600</v>
+        <v>71000</v>
       </c>
       <c r="E35" s="3">
-        <v>52900</v>
+        <v>54300</v>
       </c>
       <c r="F35" s="3">
         <v>52100</v>
@@ -1994,25 +1994,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>226100</v>
+        <v>377200</v>
       </c>
       <c r="E41" s="3">
-        <v>152700</v>
+        <v>168300</v>
       </c>
       <c r="F41" s="3">
-        <v>68400</v>
+        <v>295400</v>
       </c>
       <c r="G41" s="3">
-        <v>149100</v>
+        <v>323300</v>
       </c>
       <c r="H41" s="3">
-        <v>89400</v>
+        <v>150700</v>
       </c>
       <c r="I41" s="3">
-        <v>96100</v>
+        <v>136300</v>
       </c>
       <c r="J41" s="3">
-        <v>107600</v>
+        <v>116400</v>
       </c>
       <c r="K41" s="3">
         <v>42200</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>185100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>53100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>243700</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>186800</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>73900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>17400</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>8700</v>
@@ -2083,26 +2083,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2129,25 +2129,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>29900</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>25700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>19600</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>23900</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>409700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>195800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>317600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>357200</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>163100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>148100</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>120900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>913500</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>928200</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>1037700</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>653300</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>290800</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>318800</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>187800</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2354,13 +2354,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100300</v>
+        <v>101400</v>
       </c>
       <c r="E49" s="3">
-        <v>102600</v>
+        <v>104300</v>
       </c>
       <c r="F49" s="3">
-        <v>72100</v>
+        <v>73500</v>
       </c>
       <c r="G49" s="3">
         <v>63600</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27300</v>
+        <v>110800</v>
       </c>
       <c r="E52" s="3">
-        <v>31200</v>
+        <v>99800</v>
       </c>
       <c r="F52" s="3">
-        <v>8800</v>
+        <v>70100</v>
       </c>
       <c r="G52" s="3">
-        <v>5900</v>
+        <v>52500</v>
       </c>
       <c r="H52" s="3">
-        <v>2100</v>
+        <v>35300</v>
       </c>
       <c r="I52" s="3">
-        <v>3800</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>34400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>25400</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>14800</v>
+        <v>5248800</v>
       </c>
       <c r="E57" s="3">
-        <v>2100</v>
+        <v>4820300</v>
       </c>
       <c r="F57" s="3">
-        <v>1400</v>
+        <v>4077300</v>
       </c>
       <c r="G57" s="3">
-        <v>2500</v>
+        <v>3616700</v>
       </c>
       <c r="H57" s="3">
-        <v>1500</v>
+        <v>1782000</v>
       </c>
       <c r="I57" s="3">
-        <v>1400</v>
+        <v>1733900</v>
       </c>
       <c r="J57" s="3">
-        <v>900</v>
+        <v>1055500</v>
       </c>
       <c r="K57" s="3">
         <v>900</v>
@@ -2707,25 +2707,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>323300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>300400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>21400</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>49800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>79800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>37200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>48100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2763,8 +2763,8 @@
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
-        <v>13200</v>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>5586900</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>5122800</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>4100000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>3669000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1863400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1772500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1104500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>405000</v>
+        <v>332900</v>
       </c>
       <c r="E61" s="3">
-        <v>115700</v>
+        <v>278900</v>
       </c>
       <c r="F61" s="3">
-        <v>86400</v>
+        <v>180500</v>
       </c>
       <c r="G61" s="3">
-        <v>36000</v>
+        <v>69100</v>
       </c>
       <c r="H61" s="3">
-        <v>25000</v>
+        <v>119400</v>
       </c>
       <c r="I61" s="3">
-        <v>25000</v>
+        <v>55000</v>
       </c>
       <c r="J61" s="3">
-        <v>2700</v>
+        <v>32400</v>
       </c>
       <c r="K61" s="3">
         <v>3000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>12300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3491,7 +3491,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>572400</v>
+        <v>572300</v>
       </c>
       <c r="E76" s="3">
         <v>508600</v>
@@ -3631,10 +3631,10 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>65600</v>
+        <v>71000</v>
       </c>
       <c r="E81" s="3">
-        <v>52900</v>
+        <v>54300</v>
       </c>
       <c r="F81" s="3">
         <v>52100</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-18100</v>
+        <v>12700</v>
       </c>
       <c r="E96" s="3">
-        <v>-12200</v>
+        <v>10800</v>
       </c>
       <c r="F96" s="3">
-        <v>-9400</v>
+        <v>9400</v>
       </c>
       <c r="G96" s="3">
-        <v>-7500</v>
+        <v>7500</v>
       </c>
       <c r="H96" s="3">
-        <v>-5100</v>
+        <v>5100</v>
       </c>
       <c r="I96" s="3">
-        <v>-3300</v>
+        <v>3300</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>BFST</t>
   </si>
@@ -656,118 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>260700</v>
+      </c>
+      <c r="E8" s="3">
         <v>245800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>218000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>181600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>137800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>88300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>43400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>38600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>27500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>29000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -810,36 +816,39 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>260700</v>
+      </c>
+      <c r="E10" s="3">
         <v>245800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>218000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>181600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>137800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>45800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,36 +980,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1009,44 +1028,47 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E15" s="3">
         <v>4700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E17" s="3">
         <v>156500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>143700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>115000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>91400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>57700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5500</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E18" s="3">
         <v>89400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>74300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>66600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>30600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>36400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23500</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,8 +1212,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1206,72 +1239,78 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-29600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-27300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17900</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E21" s="3">
         <v>94000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>79100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>70800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>50700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>33100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1296,8 +1335,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1314,99 +1353,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E23" s="3">
         <v>90600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>68600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>64600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E24" s="3">
         <v>19500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E26" s="3">
         <v>71000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>54300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>52100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>30000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E27" s="3">
         <v>65600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>52900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>52100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>30000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,27 +1671,30 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>500</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,9 +1785,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1746,72 +1815,78 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>29600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>27300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17900</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E33" s="3">
         <v>71000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>54300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>52100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>30000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4800</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E35" s="3">
         <v>71000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>54300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>52100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>30000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4800</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,58 +2073,62 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>516800</v>
+      </c>
+      <c r="E41" s="3">
         <v>377200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>168300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>295400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>323300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>150700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>136300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>50800</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2060,26 +2149,29 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>8700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2104,8 +2196,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2122,36 +2214,39 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1700</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1400</v>
       </c>
       <c r="F44" s="3">
         <v>1400</v>
       </c>
       <c r="G44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H44" s="3">
         <v>9100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2167,36 +2262,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E45" s="3">
         <v>29900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>19600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2212,36 +2310,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>609700</v>
+      </c>
+      <c r="E46" s="3">
         <v>409700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>195800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>317600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>357200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>163100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>148100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>120900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2257,36 +2358,39 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>934600</v>
+      </c>
+      <c r="E47" s="3">
         <v>913500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>928200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1037700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>653300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>290800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>318800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187800</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2302,87 +2406,93 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E48" s="3">
         <v>69500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>63200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>58200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>58600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E49" s="3">
         <v>101400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>104300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>55200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>57400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,36 +2598,39 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E52" s="3">
         <v>110800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>99800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>70100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>52500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>35300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>34400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25400</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,12 +2643,15 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7857100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6584600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5990500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4726400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4160400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2273800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2094900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1321300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1105800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1076100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>684500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>684200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,80 +2785,84 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6511300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5248800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4820300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4077300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3616700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1782000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1733900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1055500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E58" s="3">
         <v>323300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>49800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>79800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>37200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2745,9 +2878,12 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2784,42 +2920,45 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6628400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5586900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5122800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4100000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3669000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1863400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1772500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1104500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2835,39 +2974,42 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>332900</v>
+        <v>400500</v>
       </c>
       <c r="E61" s="3">
+        <v>335400</v>
+      </c>
+      <c r="F61" s="3">
         <v>278900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>180500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>69100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>119400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>55000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>32400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2880,36 +3022,39 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20400</v>
+        <v>28700</v>
       </c>
       <c r="E62" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F62" s="3">
         <v>8300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4400</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7057600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5940300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5410000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4293000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3750400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1988700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1834800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1141300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>992300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>963600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>605700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>612300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3227,7 +3394,7 @@
         <v>71900</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>71900</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E72" s="3">
         <v>216100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>164000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>121900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>79200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>727500</v>
+      </c>
+      <c r="E76" s="3">
         <v>572300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>508600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>433400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>410000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>285100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>260100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>179900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>113600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>112400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>78800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>71900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E81" s="3">
         <v>71000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>54300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>52100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>30000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4800</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1200</v>
       </c>
       <c r="J83" s="3">
         <v>1200</v>
       </c>
       <c r="K83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>800</v>
       </c>
       <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>800</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E89" s="3">
         <v>92400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>69600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-294900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-521100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-675400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-475300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-192300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-170300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-153400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>16000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,35 +4454,36 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E96" s="3">
         <v>12700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>10800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>9400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>7500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4643,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>326500</v>
+      </c>
+      <c r="E100" s="3">
         <v>502100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>715300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>538200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>505700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>161200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>139500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>210900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>26500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>25600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,8 +4721,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4485,58 +4733,64 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E102" s="3">
         <v>73400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>84400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-80800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>59800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>65400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BFST_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>BFST</t>
   </si>
@@ -656,124 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>312800</v>
+      </c>
+      <c r="E8" s="3">
         <v>260700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>218000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>181600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>137800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>88300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>43400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>38600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -819,39 +825,42 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>312800</v>
+      </c>
+      <c r="E10" s="3">
         <v>260700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>245800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>218000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>181600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>137800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>88300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>45800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -867,9 +876,12 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,39 +999,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1200</v>
+        <v>3200</v>
       </c>
       <c r="E14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1031,47 +1050,50 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E15" s="3">
         <v>5300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>176400</v>
+        <v>199300</v>
       </c>
       <c r="E17" s="3">
+        <v>176000</v>
+      </c>
+      <c r="F17" s="3">
         <v>156500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>143700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>115000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>91400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>84300</v>
+        <v>113500</v>
       </c>
       <c r="E18" s="3">
+        <v>84700</v>
+      </c>
+      <c r="F18" s="3">
         <v>89400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>74300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>66600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>46300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,8 +1245,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1242,75 +1275,81 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-29600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-27300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>89500</v>
+        <v>119200</v>
       </c>
       <c r="E21" s="3">
+        <v>89900</v>
+      </c>
+      <c r="F21" s="3">
         <v>94000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>79100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>70800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>50700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>33100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1338,8 +1377,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1356,105 +1395,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>110300</v>
+      </c>
+      <c r="E23" s="3">
         <v>83100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>90600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>68600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>64600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>36800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E24" s="3">
         <v>17900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E26" s="3">
         <v>65100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>71000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>54300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>52100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>30000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E27" s="3">
         <v>59700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>65600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>52900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>52100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>30000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,27 +1734,30 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>500</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,9 +1854,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1818,75 +1887,81 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>29600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>27300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E33" s="3">
         <v>65100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>71000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>54300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>52100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>30000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4800</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E35" s="3">
         <v>65100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>71000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>54300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>52100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>30000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4800</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,65 +2159,69 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>583600</v>
+      </c>
+      <c r="E41" s="3">
         <v>516800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>377200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>168300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>295400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>323300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>150700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10100</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E42" s="3">
         <v>50800</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -2152,26 +2241,29 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>8700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2199,8 +2291,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2217,39 +2309,42 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1400</v>
       </c>
       <c r="G44" s="3">
         <v>1400</v>
       </c>
       <c r="H44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I44" s="3">
         <v>9100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2265,39 +2360,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E45" s="3">
         <v>35900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>29900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2313,39 +2411,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>661800</v>
+      </c>
+      <c r="E46" s="3">
         <v>609700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>409700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>195800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>317600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>357200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>163100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>148100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>120900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2361,39 +2462,42 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1038600</v>
+      </c>
+      <c r="E47" s="3">
         <v>934600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>913500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>928200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1037700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>653300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>290800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>318800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>187800</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2409,93 +2513,99 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E48" s="3">
         <v>82000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>63200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>58200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>58600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E49" s="3">
         <v>139700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>101400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>104300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>63600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>55200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>57400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,9 +2615,12 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,39 +2717,42 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E52" s="3">
         <v>135000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>110800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>99800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>70100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>52500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>34400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25400</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,12 +2765,15 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8214700</v>
+      </c>
+      <c r="E54" s="3">
         <v>7857100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6584600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5990500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4726400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4160400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2273800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2094900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1321300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1105800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1076100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>684500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>684200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,86 +2915,90 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6698600</v>
+      </c>
+      <c r="E57" s="3">
         <v>6511300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5248800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4820300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4077300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3616700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1782000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1733900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1055500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>284700</v>
+      </c>
+      <c r="E58" s="3">
         <v>111100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>323300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>300400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>49800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>79800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>37200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>48100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2881,9 +3014,12 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2923,45 +3059,48 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6987500</v>
+      </c>
+      <c r="E60" s="3">
         <v>6628400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5586900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5122800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4100000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3669000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1863400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1772500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1104500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2977,42 +3116,45 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>400500</v>
+        <v>293400</v>
       </c>
       <c r="E61" s="3">
+        <v>404000</v>
+      </c>
+      <c r="F61" s="3">
         <v>335400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>278900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>180500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>69100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>119400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>55000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>32400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3025,39 +3167,42 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28700</v>
+        <v>37000</v>
       </c>
       <c r="E62" s="3">
+        <v>25300</v>
+      </c>
+      <c r="F62" s="3">
         <v>17900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4400</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3073,9 +3218,12 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7317900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7057600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5940300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5410000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4293000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3750400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1988700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1834800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1141300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>992300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>963600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>605700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>612300</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3397,7 +3564,7 @@
         <v>71900</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>71900</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>326600</v>
+      </c>
+      <c r="E72" s="3">
         <v>261000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>216100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>164000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>121900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>79200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>38000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>825000</v>
+      </c>
+      <c r="E76" s="3">
         <v>727500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>572300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>508600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>433400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>410000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>285100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>260100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>179900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>113600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>112400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>78800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E81" s="3">
         <v>65100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>71000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>54300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>52100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>30000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4800</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E83" s="3">
         <v>5300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1200</v>
       </c>
       <c r="K83" s="3">
         <v>1200</v>
       </c>
       <c r="L83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>800</v>
       </c>
       <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>800</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E89" s="3">
         <v>61400</v>
       </c>
-      <c r="E89" s="3">
-        <v>92400</v>
-      </c>
       <c r="F89" s="3">
+        <v>91000</v>
+      </c>
+      <c r="G89" s="3">
         <v>69600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>56400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>8200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-281500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-294900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-521100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-675400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-475300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-192300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-170300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-153400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>16000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11900</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,38 +4687,39 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E96" s="3">
         <v>14900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>12700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>10800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>9400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>7500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1800</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,57 +4888,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>281500</v>
+      </c>
+      <c r="E100" s="3">
         <v>326500</v>
       </c>
-      <c r="E100" s="3">
-        <v>502100</v>
-      </c>
       <c r="F100" s="3">
+        <v>503500</v>
+      </c>
+      <c r="G100" s="3">
         <v>715300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>538200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>505700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>161200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>139500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>210900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>26500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>25600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4724,8 +4972,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4736,61 +4984,67 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E102" s="3">
         <v>93000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>73400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>84400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-80800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>59800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>65400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>14900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
